--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Мелитополь/дв 25,08,26 млрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Мелитополь/дв 25,08,26 млрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459202A8-1AB7-47A3-874F-35C20B696391}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EB387B-3233-4C8C-B559-EE6787B5A8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$53</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -443,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -459,9 +451,7 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -779,7 +769,7 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.140625" customWidth="1"/>
     <col min="15" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7" style="17" customWidth="1"/>
+    <col min="20" max="20" width="7" style="15" customWidth="1"/>
     <col min="21" max="22" width="5" customWidth="1"/>
     <col min="23" max="32" width="6" customWidth="1"/>
     <col min="33" max="33" width="44.28515625" customWidth="1"/>
@@ -1263,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="5"/>
-      <c r="T6" s="15"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="1">
         <f t="shared" ref="U6:U53" si="4">(F6+O6+Q6)/P6</f>
         <v>165.75428859737639</v>
@@ -1368,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="5"/>
-      <c r="T7" s="15"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
@@ -1475,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="5"/>
-      <c r="T8" s="15"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
@@ -1592,7 +1582,7 @@
         <f>VLOOKUP(A9,заказ!A:B,2,0)</f>
         <v>16</v>
       </c>
-      <c r="T9" s="15"/>
+      <c r="T9" s="1"/>
       <c r="U9" s="1">
         <f t="shared" si="4"/>
         <v>15.000000000000002</v>
@@ -1697,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="5"/>
-      <c r="T10" s="15"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -1808,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="5"/>
-      <c r="T11" s="15"/>
+      <c r="T11" s="1"/>
       <c r="U11" s="1">
         <f t="shared" si="4"/>
         <v>37.678571428571431</v>
@@ -1919,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="5"/>
-      <c r="T12" s="15"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="1">
         <f t="shared" si="4"/>
         <v>395.83333333333337</v>
@@ -2030,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="5"/>
-      <c r="T13" s="15"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="1">
         <f t="shared" si="4"/>
         <v>21.411764705882351</v>
@@ -2139,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="5"/>
-      <c r="T14" s="15"/>
+      <c r="T14" s="1"/>
       <c r="U14" s="1">
         <f t="shared" si="4"/>
         <v>54.625</v>
@@ -2256,7 +2246,7 @@
         <f>VLOOKUP(A15,заказ!A:B,2,0)</f>
         <v>32</v>
       </c>
-      <c r="T15" s="15"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="1">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -2375,7 +2365,7 @@
         <f>VLOOKUP(A16,заказ!A:B,2,0)</f>
         <v>32</v>
       </c>
-      <c r="T16" s="15"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -2490,7 +2480,7 @@
         <f>VLOOKUP(A17,заказ!A:B,2,0)</f>
         <v>32</v>
       </c>
-      <c r="T17" s="15"/>
+      <c r="T17" s="1"/>
       <c r="U17" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -2597,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="5"/>
-      <c r="T18" s="15"/>
+      <c r="T18" s="1"/>
       <c r="U18" s="1">
         <f t="shared" si="4"/>
         <v>40.294117647058826</v>
@@ -2710,7 +2700,7 @@
         <f>VLOOKUP(A19,заказ!A:B,2,0)</f>
         <v>24</v>
       </c>
-      <c r="T19" s="15"/>
+      <c r="T19" s="1"/>
       <c r="U19" s="1">
         <f t="shared" si="4"/>
         <v>13.999999999999998</v>
@@ -2823,7 +2813,7 @@
         <f>VLOOKUP(A20,заказ!A:B,2,0)</f>
         <v>670</v>
       </c>
-      <c r="T20" s="15"/>
+      <c r="T20" s="1"/>
       <c r="U20" s="1">
         <f t="shared" si="4"/>
         <v>15.000000000000002</v>
@@ -2932,7 +2922,7 @@
         <f>VLOOKUP(A21,заказ!A:B,2,0)</f>
         <v>500</v>
       </c>
-      <c r="T21" s="15">
+      <c r="T21" s="1">
         <v>1000</v>
       </c>
       <c r="U21" s="1">
@@ -3048,7 +3038,7 @@
         <f>VLOOKUP(A22,заказ!A:B,2,0)</f>
         <v>8</v>
       </c>
-      <c r="T22" s="15"/>
+      <c r="T22" s="1"/>
       <c r="U22" s="1">
         <f t="shared" si="4"/>
         <v>15.961538461538462</v>
@@ -3157,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="5"/>
-      <c r="T23" s="15"/>
+      <c r="T23" s="1"/>
       <c r="U23" s="1">
         <f t="shared" si="4"/>
         <v>14.666666666666666</v>
@@ -3266,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="5"/>
-      <c r="T24" s="15"/>
+      <c r="T24" s="1"/>
       <c r="U24" s="1">
         <f t="shared" si="4"/>
         <v>15.769230769230768</v>
@@ -3369,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="5"/>
-      <c r="T25" s="15"/>
+      <c r="T25" s="1"/>
       <c r="U25" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -3474,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="5"/>
-      <c r="T26" s="15"/>
+      <c r="T26" s="1"/>
       <c r="U26" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -3579,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="5"/>
-      <c r="T27" s="15"/>
+      <c r="T27" s="1"/>
       <c r="U27" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -3690,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="5"/>
-      <c r="T28" s="15"/>
+      <c r="T28" s="1"/>
       <c r="U28" s="1">
         <f t="shared" si="4"/>
         <v>46.304347826086961</v>
@@ -3804,7 +3794,7 @@
         <f>VLOOKUP(A29,заказ!A:B,2,0)</f>
         <v>8</v>
       </c>
-      <c r="T29" s="15"/>
+      <c r="T29" s="1"/>
       <c r="U29" s="1">
         <f t="shared" si="4"/>
         <v>15.789473684210527</v>
@@ -3917,7 +3907,7 @@
         <f>VLOOKUP(A30,заказ!A:B,2,0)</f>
         <v>8</v>
       </c>
-      <c r="T30" s="15"/>
+      <c r="T30" s="1"/>
       <c r="U30" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -4024,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="5"/>
-      <c r="T31" s="15"/>
+      <c r="T31" s="1"/>
       <c r="U31" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -4141,7 +4131,7 @@
         <f>VLOOKUP(A32,заказ!A:B,2,0)</f>
         <v>60</v>
       </c>
-      <c r="T32" s="15"/>
+      <c r="T32" s="1"/>
       <c r="U32" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -4250,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="5"/>
-      <c r="T33" s="15"/>
+      <c r="T33" s="1"/>
       <c r="U33" s="1">
         <f t="shared" si="4"/>
         <v>19.767441860465116</v>
@@ -4361,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="5"/>
-      <c r="T34" s="15"/>
+      <c r="T34" s="1"/>
       <c r="U34" s="1">
         <f t="shared" si="4"/>
         <v>15.091743119266054</v>
@@ -4478,7 +4468,7 @@
         <f>VLOOKUP(A35,заказ!A:B,2,0)</f>
         <v>40</v>
       </c>
-      <c r="T35" s="15"/>
+      <c r="T35" s="1"/>
       <c r="U35" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -4593,7 +4583,7 @@
         <f>VLOOKUP(A36,заказ!A:B,2,0)</f>
         <v>270</v>
       </c>
-      <c r="T36" s="15"/>
+      <c r="T36" s="1"/>
       <c r="U36" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -4702,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="5"/>
-      <c r="T37" s="15"/>
+      <c r="T37" s="1"/>
       <c r="U37" s="1">
         <f t="shared" si="4"/>
         <v>15.129115044247786</v>
@@ -4811,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="5"/>
-      <c r="T38" s="15"/>
+      <c r="T38" s="1"/>
       <c r="U38" s="1">
         <f t="shared" si="4"/>
         <v>19.090909090909093</v>
@@ -4920,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="5"/>
-      <c r="T39" s="15"/>
+      <c r="T39" s="1"/>
       <c r="U39" s="1">
         <f t="shared" si="4"/>
         <v>41.117647058823529</v>
@@ -5031,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="5"/>
-      <c r="T40" s="15"/>
+      <c r="T40" s="1"/>
       <c r="U40" s="1">
         <f t="shared" si="4"/>
         <v>51.816316146540032</v>
@@ -5142,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="5"/>
-      <c r="T41" s="15"/>
+      <c r="T41" s="1"/>
       <c r="U41" s="1">
         <f t="shared" si="4"/>
         <v>39.587353986795328</v>
@@ -5251,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="5"/>
-      <c r="T42" s="15"/>
+      <c r="T42" s="1"/>
       <c r="U42" s="1">
         <f t="shared" si="4"/>
         <v>18.205161306980287</v>
@@ -5360,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="5"/>
-      <c r="T43" s="15"/>
+      <c r="T43" s="1"/>
       <c r="U43" s="1">
         <f t="shared" si="4"/>
         <v>37.181587837837846</v>
@@ -5469,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="5"/>
-      <c r="T44" s="15"/>
+      <c r="T44" s="1"/>
       <c r="U44" s="1">
         <f t="shared" si="4"/>
         <v>57.826086956521742</v>
@@ -5578,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="5"/>
-      <c r="T45" s="15"/>
+      <c r="T45" s="1"/>
       <c r="U45" s="1">
         <f t="shared" si="4"/>
         <v>76.17647058823529</v>
@@ -5689,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="5"/>
-      <c r="T46" s="15"/>
+      <c r="T46" s="1"/>
       <c r="U46" s="1">
         <f t="shared" si="4"/>
         <v>29.833333333333332</v>
@@ -5798,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="5"/>
-      <c r="T47" s="16"/>
+      <c r="T47" s="9"/>
       <c r="U47" s="9">
         <f t="shared" si="4"/>
         <v>12.909090909090908</v>
@@ -5909,7 +5899,7 @@
         <f>VLOOKUP(A48,заказ!A:B,2,0)</f>
         <v>20</v>
       </c>
-      <c r="T48" s="15"/>
+      <c r="T48" s="1"/>
       <c r="U48" s="1">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -6016,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="5"/>
-      <c r="T49" s="15"/>
+      <c r="T49" s="1"/>
       <c r="U49" s="1">
         <f t="shared" si="4"/>
         <v>25.960427623070956</v>
@@ -6127,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="5"/>
-      <c r="T50" s="16"/>
+      <c r="T50" s="9"/>
       <c r="U50" s="9">
         <f t="shared" si="4"/>
         <v>44.347826086956523</v>
@@ -6234,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="5"/>
-      <c r="T51" s="15"/>
+      <c r="T51" s="1"/>
       <c r="U51" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
@@ -6346,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="5"/>
-      <c r="T52" s="15"/>
+      <c r="T52" s="1"/>
       <c r="U52" s="1">
         <f t="shared" si="4"/>
         <v>23.653809829624873</v>
@@ -6451,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="5"/>
-      <c r="T53" s="16"/>
+      <c r="T53" s="9"/>
       <c r="U53" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
